--- a/赛事清单/北京赛事清单_2026年11月至2027春节.xlsx
+++ b/赛事清单/北京赛事清单_2026年11月至2027春节.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -51,13 +51,6 @@
       <b val="1"/>
       <color rgb="FFC00000"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
@@ -539,153 +532,153 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -711,27 +704,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -855,6 +827,214 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1140,12 +1320,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1719,19 +1899,940 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="33" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>越野跑山</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>第二十六届京西三峰连穿越野赛</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>11月15日</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>海淀区·大觉寺</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>10月28日</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>最酷平台报名（zuicool.com搜索赛事名）；经典三峰连穿线路，10月28日截止</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="33" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>越野跑山</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>第十五届海淀之巅三峰越野赛</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>12月6日</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>海淀区·大觉寺</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>10月28日</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>最酷平台报名；海淀三峰经典赛道，10月28日截止</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="33" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>跑步</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>公园半马北京公开赛·哲思狐第九届高校1+1接力</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>11月8日</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>昌平区·白浮泉公园</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>10月28日</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>最酷平台报名；高校1+1接力形式，10月28日截止</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="33" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>越野跑山</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>2026跨越山海·中韩同行BLACKYAK延寿越野赛</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>11月8日</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>昌平区·延寿镇海字桥</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>10月28日18:00</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>最酷平台报名；昌平秋季大型越野赛，10月28日18时截止</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="33" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>越野跑山</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>2026西山越野荟·北京模式口站</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>11月22日</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>石景山区·模式口公园</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>10月31日</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>最酷平台报名；自10月18日延期至11月22日举办，设万元奖金</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="33" customHeight="1">
+      <c r="A20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>户外徒步</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>第二届西山红枫逐梦徒步大会</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>11月8日</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>海淀区·西山国家森林公园</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>11月1日</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>最酷平台报名；秋季赏红叶徒步活动</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="33" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>越野跑山</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>2026启航越野训练赛第46期—香山站（ITRA/UTMB积分赛）</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>11月8日</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>海淀区·香山诗书园</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>11月2日</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>最酷平台报名；ITRA/UTMB积分赛，十二生肖系列奖牌任选</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="33" customHeight="1">
+      <c r="A22" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>跑步</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>第三届奥森长跑节（全民健康跑系列）</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>11月15日</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>朝阳区·奥森北园南门</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>11月3日</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>最酷平台报名</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="33" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>越野跑山</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>2026思凯乐瓢虫越野训练赛·北京模式口深秋赛</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>11月14日</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>石景山区·模式口公园</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>11月4日</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>最酷平台报名；短距离越野训练赛</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="33" customHeight="1">
+      <c r="A24" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>跑步</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>2026野鸭湖冬季健康跑</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>11月15日</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>延庆区·野鸭湖湿地公园</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>11月8日</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>最酷平台报名；北京最大湿地公园冬季路跑</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="33" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>越野跑山</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>2026京西古道越野赛</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>11月22日</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>海淀区·香山玉皇顶</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>11月10日</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>最酷平台报名；起终点信息以赛事页为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="33" customHeight="1">
+      <c r="A26" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>跑步</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>第三届京南长跑节（全民健康跑系列）</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>11月22日</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>大兴区·南海子公园二期</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>11月10日</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>最酷平台报名</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="33" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>骑行</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>拓路者2026北京香山爬坡赛</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>12月6日</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>海淀区·香山玉皇百果生态园</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>11月6日</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>最酷平台报名；品类以赛事页为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="33" customHeight="1">
+      <c r="A28" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>户外徒步</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>马绘西山—2026西山晚秋福马徒步大会</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>11月29日</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>海淀区·西山国家森林公园东门</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>11月22日</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>最酷平台报名；晚秋徒步赏景</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="33" customHeight="1">
+      <c r="A29" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>越野跑山</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>2026北京山峰逐峰行</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>12月12日</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>海淀区·大觉寺</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>汇跑体育（爱汇跑平台）报名，208-398元</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="33" customHeight="1">
+      <c r="A30" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>跑步</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>锐进四季·第三届元旦迎新跑</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>2027年1月1日</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>朝阳区·奥森北园西门广场</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>12月16日</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>最酷平台报名；元旦跨年跑</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="33" customHeight="1">
+      <c r="A31" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>跑步</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>2027天成悦行第四届奥森迎新跑</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>2027年1月1日</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>朝阳区·奥森北园南门</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>12月18日</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>最酷平台报名；元旦跨年跑</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="33" customHeight="1">
+      <c r="A32" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>跑步</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>锐进四季—第三届元旦亲子迎新跑</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>2027年1月1日</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>朝阳区·奥森北园西门广场</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>12月25日</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>最酷平台报名；含亲子组</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="33" customHeight="1">
+      <c r="A33" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>武术搏击</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>2026年北京第23届少儿武术冠军赛</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>11月21日</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>国家奥林匹克体育中心体育馆</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>11月9日</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>少儿武术官方站（shaoerwushu.org）报名；青少年赛事</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="33" customHeight="1">
+      <c r="A34" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>乒乓球</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>“李宁杯”第三十二届北京市乒乓球协会杯比赛</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>11月14-15日</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>通州区·李宁体育中心</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>以官宣为准</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>官宣确认</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>北京市体育总会官宣（11月14-15日通州李宁中心开赛）；组队参赛详情盯市乒协后续通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="33" customHeight="1">
+      <c r="A35" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>网球</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>2026中国大众网球城市挑战赛全国总决赛</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>11月26-29日</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>朝阳区·国家网球中心</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>11月14日</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>中国网球协会官网10月27日通知：10月28日开启报名、11月14日截止；混团运动员8-10人，官网报名</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="33" customHeight="1">
+      <c r="A36" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>电子竞技</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>2026动感地带校园电竞联赛秋季赛</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>11月海选至12月初总决赛</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>线上+高校赛场</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>线上海选持续</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>免费报名；全国在校大学生，王者荣耀/和平精英/无畏契约等五项目（千龙网9月30日报道）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="33" customHeight="1">
+      <c r="A37" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>足球</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>2026年百队杯精英联赛（十一人制）</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>10月25日至12月</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>各赛区</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>10月12日已截止</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>北京市足协（bfaweb.cn）；青少年赛事，10月25日已开赛</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -1982,13 +3083,434 @@
         </is>
       </c>
     </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>待官宣</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>第十二届大众冰雪北京公开赛·北京滑雪登山公开赛</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>预计12月报名、2027年1月1日开赛</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>延庆区·国家高山滑雪中心（参照去年）</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>9月30日承办已中标（北京梦起源体育），报名预计12月开启，盯北京市登山运动协会</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>待官宣</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>第十二届大众冰雪北京公开赛·京张冰钓比赛</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>预计12月中旬报名、2027年1月中开赛</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>延庆区·金隅八达岭温泉度假村（参照去年）</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>9月20日比选公告已出；报名走北京市钓鱼协会公众号/小程序，参照去年120人规模</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>待官宣</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>2027全国新年登高健身大会北京主会场暨居庸关长城垂直挑战赛</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>预计12月中旬报名、2027年1月1日开赛</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>昌平区·居庸关长城</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>年度固定赛事，去年规模2000人分三组、超员抽签；预计12月10日前后报名，盯“运动帮助手”小程序/马拉马拉/最酷</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>待官宣</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>第十三届北京市民快乐冰雪季系列活动（冰雪大联动等）</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>预计2027年1月启动</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>石景山区·首钢园等（参照去年）</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>去年第十二届1月31日首钢园大跳台启动并发布冰雪护照；今年届次+1，盯北京市社会体育管理中心</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>待官宣</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>北京市滑雪定向公开赛（今年届次）</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>预计2027年1月初报名</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>密云区·云佛山滑雪场</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>官方确认第三届筹备已进入尾声、官宣在即；往届1月初密云云佛山滑雪场、限200人，设亲子/公开男女组</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>待官宣</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>副中心&amp;北三县3V3篮球赛（新届）</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>预计12月报名、1月开赛</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>通州区（参照去年）</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>去年12月4日截止报名、冠军奖金1万元；今年届次待官宣，盯通州区体育局</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>观赛</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>奥森冰雪嘉年华等冰雪乐园（快乐冰雪季配套）</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>预计12月下旬开园</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>朝阳区·奥林匹克森林公园</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>去年12月底开园，偏游乐观赛体验；另IEM北京11月2-8日五棵松CS2职业赛需另行购票</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>待官宣</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>第四届北京攀冰公开赛</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>预计12月上旬报名、2027年1月办赛</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>延庆区·玉渡山攀冰基地（参照去年）</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>去年第三届报名12月9日-1月9日，亚洲金冰镐奖得主周鹏担任技术总监定线；盯北京市登山运动协会</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>待官宣</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>北京TOP短道速滑国际公开赛（新赛季）</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>预计11月底至12月多站</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>世纪星国际冰雪体育中心、国家速滑馆（参照去年）</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>去年11月29日-12月28日连办三站，大众参与型赛事，站次官宣后可报名；盯快乐冰雪季系列发布</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>待官宣</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>第十二届大众冰雪北京公开赛·成人冰球比赛</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>预计2027年2月（春节档）</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>朝阳区·国家体育馆冰球馆（参照去年）</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>去年为2月1日-28日举办；冰雪公开赛系列延续，正好填补春节档空窗，盯系列公告</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>待官宣</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>第二届石景山大众越野滑雪挑战赛</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>预计2027年2月（春节档）</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>石景山区·永定河冰雪世界</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>去年2月8-9日办赛（体验组+运动组，免费入园）；单源报道，盯石景山区体育局</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>待官宣</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>南山公开赛（单板/双板，新赛季）</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>预计2027年1月</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>密云区·南山滑雪场</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>国内顶尖业余滑雪品牌赛，去年第十届1月25日办并含World Rookie Tour国际青少组；盯南山滑雪场官网</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>观赛</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>什刹海冰场/什刹海冰雪嘉年华</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>预计1月中旬全面开放</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>西城区·什刹海前海后海</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>去年1月20日全开，13.5万㎡冰面含2万㎡速滑区，冰车冰滑梯+冰球速滑花滑培训；体验观赛两宜</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>观赛</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>昆仑决世界格斗冠军赛（怀柔春节档）</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>预计2027年2月下旬</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>怀柔区·雁栖湖国际会展中心（参照去年）</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>去年2月21-22日首次登陆，设洲际/世界金腰带主赛；购票观赛，今年档期待官宣（单源）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2055,12 +3577,12 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>空窗（冬训季）</t>
+          <t>11月-元旦密集档</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>北马10月收官，11月半马档（朝阳滨河半马等）已截止；12月起无大型路跑，转线上赛/冬训</t>
+          <t>商业路跑密集：奥森长跑节11.15、京南长跑节11.22、野鸭湖冬跑11.15、元旦迎新跑三连（奥森）——北马后仍有大量中小型路跑</t>
         </is>
       </c>
     </row>
@@ -2075,12 +3597,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>空窗</t>
+          <t>单点窗口</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>室外骑行赛季10月收官，冬季以骑行台训练为主；春季档3-4月重启</t>
+          <t>拓路者香山爬坡赛12.6报名中（最酷平台）；室外骑行赛季基本收官，春季档3-4月重启</t>
         </is>
       </c>
     </row>
@@ -2095,12 +3617,12 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>空窗</t>
+          <t>网球单点窗口</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>室外季节性项目收官，春季档重启；室内场馆约球走俱乐部渠道</t>
+          <t>大众网球城市挑战赛总决赛11.26-29国家网球中心（报名待核）；飞盘/腰旗仍空窗，春季档重启</t>
         </is>
       </c>
     </row>
@@ -2120,7 +3642,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>第十二届冰雪公开赛系列12月-1月（滑雪登山/攀冰/冰钓/雪垒/成人冰球），冰钓承办公告已出——北京冬季最大增量档</t>
+          <t>第十二届冰雪公开赛系列12月-2月（滑雪登山/攀冰/冰钓/雪垒/成人冰球/越野滑雪挑战赛），滑雪登山9.30已中标、冰钓9.20已比选、滑雪定向第三届筹备收尾——北京冬季最大增量档，具体赛详见待官宣页</t>
         </is>
       </c>
     </row>
@@ -2235,12 +3757,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>单点窗口</t>
+          <t>窗口扩大</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>体育大会空手道12月（预计）；中国式摔跤10月初已完赛</t>
+          <t>少儿武术冠军赛11.21奥体中心（报名至11.9）+体育大会空手道12月（预计）；中国式摔跤10月初已完赛</t>
         </is>
       </c>
     </row>
@@ -2275,27 +3797,28 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>观赛窗口</t>
+          <t>观赛+校园报名</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>IEM北京11月2-8日五棵松（国际顶级CS2），职业赛不开放报名，购票观赛</t>
+          <t>IEM北京11月2-8日五棵松（CS2职业赛，购票观赛）；动感地带校园电竞联赛11月海选、12月初总决赛（大学生免费报名）</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -2398,7 +3921,36 @@
         </is>
       </c>
     </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>· 10月27日二次深挖：新增30场（可报名23场+待官宣7场），并修正跑步/骑行/网球/武术/电竞空窗判定；主要来源：最酷/爱汇跑等商业报名平台、北京市体育总会招标公告、市足协/少儿武术官方站、千龙网，</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  商业赛事信息以平台页面为准，“待核实”赛事需再盯官宣；最紧急硬截止：京西三峰/海淀之巅/高校接力/延寿越野均为10月28日，其次武术11月9日、京西古道11月10日</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>· 10月27日二轮查漏：新增待官宣/观赛7条（攀冰/TOP短道速滑/成人冰球/石景山越野滑雪/南山公开赛/什刹海冰场/昆仑决），春节档（2027年2月）从0条补至3条线索；</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  网球总决赛确认10月28日开启报名、11月14日截止（官网实锤），乒协杯获市体育总会官宣，棋类大赛确认报名渠道为小程序【汇智弈】</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>